--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_86_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_86_R9.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3086</v>
+        <v>5.6413</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8376</v>
+        <v>5.9686</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.529</v>
+        <v>-0.3274</v>
       </c>
       <c r="G2" t="n">
         <v>3.2973</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0113</v>
+        <v>0.344</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2388</v>
+        <v>0.3699</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2275</v>
+        <v>-0.0259</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0934</v>
+        <v>4.5111</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2253</v>
+        <v>4.7102</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1318</v>
+        <v>-0.1991</v>
       </c>
       <c r="G3" t="n">
         <v>2.9447</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3627</v>
+        <v>0.7804</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8259</v>
+        <v>0.3108</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.4696</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2052</v>
+        <v>2.5667</v>
       </c>
       <c r="E4" t="n">
         <v>1.1916</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0136</v>
+        <v>1.3751</v>
       </c>
       <c r="G4" t="n">
         <v>0.3746</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0625</v>
+        <v>1.424</v>
       </c>
       <c r="T4" t="n">
         <v>0.3383</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7243</v>
+        <v>1.0857</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4152</v>
+        <v>1.4324</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1121</v>
+        <v>1.23</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3031</v>
+        <v>0.2023</v>
       </c>
       <c r="G5" t="n">
         <v>0.0805</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0993</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2434</v>
+        <v>-0.1254</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3255</v>
+        <v>0.2247</v>
       </c>
       <c r="V5" t="n">
         <v>0.7886</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2538</v>
+        <v>0.6387</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5301</v>
+        <v>1.4831</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2763</v>
+        <v>-0.8444</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9636</v>
+        <v>-0.6645</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2582</v>
+        <v>0.3827</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2946</v>
+        <v>-1.0472</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3063</v>
+        <v>0.9478</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2156</v>
+        <v>1.6237</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0907</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2699</v>
+        <v>-1.6123</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4738</v>
+        <v>-1.241</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7961</v>
+        <v>-0.3713</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4983</v>
+        <v>0.2311</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3293</v>
+        <v>0.0868</v>
       </c>
       <c r="U6" t="n">
-        <v>1.169</v>
+        <v>0.1443</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6468</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>1.214</v>
+        <v>1.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5671</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.387</v>
+        <v>-0.194</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6011</v>
+        <v>0.5865</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2141</v>
+        <v>-0.7804</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6645</v>
+        <v>-0.9636</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3827</v>
+        <v>-1.2582</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0472</v>
+        <v>0.2946</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9478</v>
+        <v>1.3063</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6237</v>
+        <v>0.2156</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6758999999999999</v>
+        <v>1.0907</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6123</v>
+        <v>-2.2699</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.241</v>
+        <v>-1.4738</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>-0.7961</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0207</v>
+        <v>1.0506</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2047</v>
+        <v>0.3857</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2254</v>
+        <v>0.6649</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>0.6468</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6083</v>
+        <v>1.214</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>-0.5671</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9361</v>
+        <v>-1.7326</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7594</v>
+        <v>-0.6232</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1766</v>
+        <v>-1.1094</v>
       </c>
       <c r="G8" t="n">
         <v>2.5892</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3681</v>
+        <v>0.8353</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8962</v>
+        <v>0.2401</v>
       </c>
       <c r="U8" t="n">
-        <v>0.528</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.214</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6691</v>
+        <v>-4.0047</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4753</v>
+        <v>-0.8109</v>
       </c>
       <c r="F9" t="n">
         <v>-3.1938</v>
@@ -1156,10 +1156,10 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2478</v>
+        <v>0.4167</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6721</v>
+        <v>-0.0077</v>
       </c>
       <c r="U9" t="n">
         <v>0.4244</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9568</v>
+        <v>-5.4109</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2706</v>
+        <v>-2.96</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6862</v>
+        <v>-2.4509</v>
       </c>
       <c r="G10" t="n">
         <v>-5.4928</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6058</v>
+        <v>-0.06</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1687</v>
+        <v>0.1419</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4371</v>
+        <v>-0.2018</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.5821</v>
+        <v>-6.5555</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8627</v>
+        <v>-5.2729</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7195</v>
+        <v>-1.2826</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9434</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5485</v>
+        <v>-0.5219</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0297</v>
+        <v>-0.44</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5188</v>
+        <v>-0.0819</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3943</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.480899999999998</v>
+        <v>-3.107499999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>5.129799999999998</v>
+        <v>5.503</v>
       </c>
       <c r="F12" t="n">
         <v>-8.6106</v>
@@ -1390,13 +1390,13 @@
         <v>10.4381</v>
       </c>
       <c r="S12" t="n">
-        <v>4.226</v>
+        <v>4.599500000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9268999999999992</v>
+        <v>1.3004</v>
       </c>
       <c r="U12" t="n">
-        <v>3.299199999999999</v>
+        <v>3.2993</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7089999999999996</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7697</v>
+        <v>4.3814</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4013</v>
+        <v>4.9797</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3684</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>3.394</v>
+        <v>2.1868</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5498</v>
+        <v>-1.8885</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8442</v>
+        <v>4.0753</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9486</v>
+        <v>4.3533</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5194</v>
+        <v>-0.0463</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4291</v>
+        <v>4.3996</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5546</v>
+        <v>-2.1665</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9696</v>
+        <v>-1.8422</v>
       </c>
       <c r="O13" t="n">
-        <v>0.415</v>
+        <v>-0.3243</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2186</v>
+        <v>-0.6614</v>
       </c>
       <c r="T13" t="n">
-        <v>0.311</v>
+        <v>-0.7503</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9076</v>
+        <v>0.089</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4665</v>
+        <v>3.7837</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1418</v>
+        <v>4.8559</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7631</v>
+        <v>3.8224</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5079</v>
+        <v>3.8116</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7448</v>
+        <v>0.0108</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1868</v>
+        <v>3.394</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8885</v>
+        <v>0.5498</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0753</v>
+        <v>2.8442</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3533</v>
+        <v>3.9486</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0463</v>
+        <v>1.5194</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3996</v>
+        <v>2.4291</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1665</v>
+        <v>-0.5546</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8422</v>
+        <v>-0.9696</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3243</v>
+        <v>0.415</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2797</v>
+        <v>0.2713</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2221</v>
+        <v>-0.2787</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0575</v>
+        <v>0.55</v>
       </c>
       <c r="V14" t="n">
-        <v>3.7837</v>
+        <v>-1.4665</v>
       </c>
       <c r="W14" t="n">
-        <v>4.8559</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2629</v>
+        <v>3.5946</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6791</v>
+        <v>3.797</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4162</v>
+        <v>-0.2025</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0515</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2913</v>
+        <v>0.0404</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4753</v>
+        <v>-0.3574</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1841</v>
+        <v>0.3978</v>
       </c>
       <c r="V15" t="n">
         <v>1.7501</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. MAKOUNDOU</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2991</v>
+        <v>1.6546</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4252</v>
+        <v>0.7305</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8739</v>
+        <v>0.9241</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6783</v>
+        <v>1.2418</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.4512</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1406</v>
+        <v>1.693</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5746</v>
+        <v>0.9741</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.6687</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0368</v>
+        <v>1.6428</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1038</v>
+        <v>0.2678</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1038</v>
+        <v>0.0502</v>
       </c>
       <c r="P16" t="n">
         <v>0.4639</v>
@@ -1702,13 +1702,13 @@
         <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1568</v>
+        <v>-0.0512</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1494</v>
+        <v>-0.2436</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3062</v>
+        <v>0.1924</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>Y. MAKOUNDOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0318</v>
+        <v>1.3162</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3766</v>
+        <v>0.5432</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6552</v>
+        <v>0.773</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2418</v>
+        <v>0.6783</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4512</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.693</v>
+        <v>0.1406</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9741</v>
+        <v>0.5746</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6687</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6428</v>
+        <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2678</v>
+        <v>0.1038</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0502</v>
+        <v>0.1038</v>
       </c>
       <c r="P17" t="n">
         <v>0.4639</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6739000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>-0.0314</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0764</v>
+        <v>0.2054</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6575</v>
+        <v>0.5657</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0157</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3582</v>
+        <v>1.1096</v>
       </c>
       <c r="G18" t="n">
         <v>0.3628</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5564</v>
+        <v>-0.3332</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1949</v>
+        <v>-0.7231</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3615</v>
+        <v>0.3899</v>
       </c>
       <c r="V18" t="n">
         <v>0.5361</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.476</v>
+        <v>-1.6861</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1861</v>
+        <v>0.2151</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6621</v>
+        <v>-1.9012</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1591</v>
+        <v>2.3817</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6037</v>
+        <v>1.9602</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5553</v>
+        <v>0.4216</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5068</v>
+        <v>4.323</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3228</v>
+        <v>3.7377</v>
       </c>
       <c r="L19" t="n">
-        <v>0.184</v>
+        <v>0.5854</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6659</v>
+        <v>-1.9413</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9265</v>
+        <v>-1.7775</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.1638</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1316</v>
+        <v>-1.3719</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5375</v>
+        <v>-0.6286</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4059</v>
+        <v>-0.7433</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1517</v>
+        <v>-2.0496</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.245</v>
+        <v>-2.7732</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0933</v>
+        <v>0.7236</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3835</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.5063</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>-0.4991</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3624</v>
+        <v>-0.0072</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7971</v>
+        <v>-2.639</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4926</v>
+        <v>0.8887</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3045</v>
+        <v>-3.5277</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3817</v>
+        <v>-1.1591</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9602</v>
+        <v>-0.6037</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4216</v>
+        <v>-0.5553</v>
       </c>
       <c r="J21" t="n">
-        <v>4.323</v>
+        <v>0.5068</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7377</v>
+        <v>0.3228</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5854</v>
+        <v>0.184</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9413</v>
+        <v>-1.6659</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7775</v>
+        <v>-0.9265</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1638</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.4829</v>
+        <v>-0.0314</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3364</v>
+        <v>0.2401</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1466</v>
+        <v>-0.2715</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5634</v>
+        <v>-3.9065</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8181</v>
+        <v>-2.6437</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7453</v>
+        <v>-1.2628</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1325</v>
@@ -2170,13 +2170,13 @@
         <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1595</v>
+        <v>-0.1836</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7986</v>
+        <v>-0.027</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6392</v>
+        <v>-0.1566</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7501</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.4809</v>
+        <v>5.053700000000003</v>
       </c>
       <c r="E23" t="n">
-        <v>9.004800000000001</v>
+        <v>9.004999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.5239</v>
+        <v>-3.9514</v>
       </c>
       <c r="G23" t="n">
-        <v>3.518800000000001</v>
+        <v>3.518799999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6245999999999998</v>
+        <v>0.6246</v>
       </c>
       <c r="I23" t="n">
         <v>2.8942</v>
@@ -2248,22 +2248,22 @@
         <v>13.9172</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.2261</v>
+        <v>-2.6533</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.2994</v>
+        <v>-3.2991</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9268</v>
+        <v>0.6459000000000003</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7089000000000001</v>
+        <v>0.7089000000000005</v>
       </c>
       <c r="W23" t="n">
         <v>8.639700000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.930800000000001</v>
+        <v>-7.9308</v>
       </c>
     </row>
   </sheetData>
